--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486321_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486321_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.2065</v>
+        <v>9.8453</v>
       </c>
       <c r="E2" t="n">
-        <v>8.013500000000001</v>
+        <v>8.529</v>
       </c>
       <c r="F2" t="n">
-        <v>1.193</v>
+        <v>1.3163</v>
       </c>
       <c r="G2" t="n">
         <v>6.5148</v>
@@ -610,13 +610,13 @@
         <v>1.0875</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.09089999999999999</v>
+        <v>0.548</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.822</v>
+        <v>-0.3064</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7311</v>
+        <v>0.8544</v>
       </c>
       <c r="V2" t="n">
         <v>1.695</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.0975</v>
+        <v>6.5302</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6154</v>
+        <v>4.5721</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4821</v>
+        <v>1.9581</v>
       </c>
       <c r="G3" t="n">
         <v>3.2938</v>
@@ -688,13 +688,13 @@
         <v>1.7401</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6731</v>
+        <v>1.1059</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1971</v>
+        <v>0.1538</v>
       </c>
       <c r="U3" t="n">
-        <v>1.476</v>
+        <v>0.952</v>
       </c>
       <c r="V3" t="n">
         <v>0.3904</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. COULIBALY</t>
+          <t>S. CECCARDI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.5078</v>
+        <v>5.5341</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5629</v>
+        <v>5.6898</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9449</v>
+        <v>-0.1557</v>
       </c>
       <c r="G4" t="n">
-        <v>4.8326</v>
+        <v>4.0131</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8955</v>
+        <v>4.3127</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9371</v>
+        <v>-0.2996</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6843</v>
+        <v>4.0713</v>
       </c>
       <c r="K4" t="n">
-        <v>1.9193</v>
+        <v>4.0331</v>
       </c>
       <c r="L4" t="n">
-        <v>0.765</v>
+        <v>0.0382</v>
       </c>
       <c r="M4" t="n">
-        <v>2.1483</v>
+        <v>-0.0583</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9761</v>
+        <v>0.2796</v>
       </c>
       <c r="O4" t="n">
-        <v>1.1722</v>
+        <v>-0.3379</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2175</v>
+        <v>-0.435</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="S4" t="n">
-        <v>2.3924</v>
+        <v>0.2611</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0106</v>
+        <v>-0.119</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3818</v>
+        <v>0.38</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.4997</v>
+        <v>1.695</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9554</v>
+        <v>2.8249</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.4552</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. CECCARDI</t>
+          <t>B. COULIBALY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.2729</v>
+        <v>4.4549</v>
       </c>
       <c r="E5" t="n">
-        <v>5.3978</v>
+        <v>2.8491</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1249</v>
+        <v>1.6059</v>
       </c>
       <c r="G5" t="n">
-        <v>4.0131</v>
+        <v>4.8326</v>
       </c>
       <c r="H5" t="n">
-        <v>4.3127</v>
+        <v>2.8955</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2996</v>
+        <v>1.9371</v>
       </c>
       <c r="J5" t="n">
-        <v>4.0713</v>
+        <v>2.6843</v>
       </c>
       <c r="K5" t="n">
-        <v>4.0331</v>
+        <v>1.9193</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0382</v>
+        <v>0.765</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0583</v>
+        <v>2.1483</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2796</v>
+        <v>0.9761</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3379</v>
+        <v>1.1722</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.435</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0001</v>
+        <v>1.3396</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.411</v>
+        <v>0.2968</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4108</v>
+        <v>1.0428</v>
       </c>
       <c r="V5" t="n">
-        <v>1.695</v>
+        <v>-1.4997</v>
       </c>
       <c r="W5" t="n">
-        <v>2.8249</v>
+        <v>0.9554</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.13</v>
+        <v>-2.4552</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. TAMBA VILLEN</t>
+          <t>S. LLORENTE PAZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.068</v>
+        <v>3.5052</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1486</v>
+        <v>1.8001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9194</v>
+        <v>1.7051</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7802</v>
+        <v>3.9099</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6111</v>
+        <v>1.4476</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3913</v>
+        <v>2.4623</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6846</v>
+        <v>3.7036</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5776</v>
+        <v>1.3504</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2622</v>
+        <v>2.3531</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0956</v>
+        <v>0.2063</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0335</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1291</v>
+        <v>0.1091</v>
       </c>
       <c r="P6" t="n">
-        <v>0.87</v>
+        <v>-0</v>
       </c>
       <c r="Q6" t="n">
+        <v>-2.1751</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.1751</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.9205</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.2716</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.6489</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-1.3252</v>
+      </c>
+      <c r="W6" t="n">
         <v>0</v>
       </c>
-      <c r="R6" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.2878</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.3341</v>
-      </c>
-      <c r="U6" t="n">
-        <v>-0.0463</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.13</v>
-      </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. LLORENTE PAZ</t>
+          <t>I. TAMBA VILLEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.7661</v>
+        <v>2.8868</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0611</v>
+        <v>1.8134</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7051</v>
+        <v>1.0735</v>
       </c>
       <c r="G7" t="n">
-        <v>3.9099</v>
+        <v>0.7802</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4476</v>
+        <v>-0.6111</v>
       </c>
       <c r="I7" t="n">
-        <v>2.4623</v>
+        <v>1.3913</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7036</v>
+        <v>0.6846</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3504</v>
+        <v>-0.5776</v>
       </c>
       <c r="L7" t="n">
-        <v>2.3531</v>
+        <v>1.2622</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2063</v>
+        <v>0.0956</v>
       </c>
       <c r="N7" t="n">
-        <v>0.09710000000000001</v>
+        <v>-0.0335</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1091</v>
+        <v>0.1291</v>
       </c>
       <c r="P7" t="n">
-        <v>-0</v>
+        <v>0.87</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1751</v>
+        <v>0.87</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1815</v>
+        <v>0.1067</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4675</v>
+        <v>-0.0012</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6489</v>
+        <v>0.1078</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.3252</v>
+        <v>1.13</v>
       </c>
       <c r="W7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X7" t="n">
         <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-1.3252</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. LARSEN</t>
+          <t>T. RICHARDSON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9626</v>
+        <v>1.9397</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0718</v>
+        <v>1.4247</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1092</v>
+        <v>0.5149</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3476</v>
+        <v>0.4684</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.0281</v>
+        <v>1.0342</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6805</v>
+        <v>-0.5658</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2192</v>
+        <v>0.7092000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.9482</v>
+        <v>0.9371</v>
       </c>
       <c r="L8" t="n">
-        <v>1.1674</v>
+        <v>-0.2279</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5668</v>
+        <v>-0.2408</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0799</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4869</v>
+        <v>-0.3379</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2175</v>
+        <v>1.9576</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>1.9576</v>
       </c>
       <c r="S8" t="n">
-        <v>1.8327</v>
+        <v>1.4039</v>
       </c>
       <c r="T8" t="n">
-        <v>1.7677</v>
+        <v>0.5203</v>
       </c>
       <c r="U8" t="n">
-        <v>0.065</v>
+        <v>0.8835</v>
       </c>
       <c r="V8" t="n">
-        <v>1.695</v>
+        <v>-1.8902</v>
       </c>
       <c r="W8" t="n">
-        <v>2.2599</v>
+        <v>0.1952</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-2.0854</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. RICHARDSON</t>
+          <t>K. LARSEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.243</v>
+        <v>1.3643</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5739</v>
+        <v>1.1345</v>
       </c>
       <c r="F9" t="n">
-        <v>0.669</v>
+        <v>0.2299</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4684</v>
+        <v>-1.3476</v>
       </c>
       <c r="H9" t="n">
-        <v>1.0342</v>
+        <v>-2.0281</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5658</v>
+        <v>0.6805</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7092000000000001</v>
+        <v>0.2192</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9371</v>
+        <v>-0.9482</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.2279</v>
+        <v>1.1674</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2408</v>
+        <v>-1.5668</v>
       </c>
       <c r="N9" t="n">
-        <v>0.09710000000000001</v>
+        <v>-1.0799</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3379</v>
+        <v>-0.4869</v>
       </c>
       <c r="P9" t="n">
-        <v>1.9576</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R9" t="n">
         <v>1.9576</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7072000000000001</v>
+        <v>1.2344</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3305</v>
+        <v>0.8304</v>
       </c>
       <c r="U9" t="n">
-        <v>1.0377</v>
+        <v>0.4041</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.8902</v>
+        <v>1.695</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1952</v>
+        <v>2.2599</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.0854</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. WALKER</t>
+          <t>M. TORRES CUEVAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2563</v>
+        <v>0.9631</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.542</v>
+        <v>-0.8458</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7983</v>
+        <v>1.809</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7621</v>
+        <v>1.4432</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7146</v>
+        <v>0.9093</v>
       </c>
       <c r="I10" t="n">
-        <v>3.4767</v>
+        <v>0.5339</v>
       </c>
       <c r="J10" t="n">
-        <v>3.2858</v>
+        <v>1.268</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.08169999999999999</v>
+        <v>1.0767</v>
       </c>
       <c r="L10" t="n">
-        <v>3.3676</v>
+        <v>0.1912</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5237000000000001</v>
+        <v>0.1752</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6328</v>
+        <v>-0.1674</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1091</v>
+        <v>0.3426</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.0451</v>
+        <v>-0.435</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.3501</v>
+        <v>-2.1751</v>
       </c>
       <c r="R10" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0257</v>
+        <v>0.1502</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6729000000000001</v>
+        <v>0.0613</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6472</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5649999999999999</v>
+        <v>-0.1952</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3698</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. TORRES CUEVAS</t>
+          <t>J. WALKER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1895</v>
+        <v>0.9568</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2496</v>
+        <v>-1.0265</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4391</v>
+        <v>1.9833</v>
       </c>
       <c r="G11" t="n">
-        <v>1.4432</v>
+        <v>2.7621</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9093</v>
+        <v>-0.7146</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5339</v>
+        <v>3.4767</v>
       </c>
       <c r="J11" t="n">
-        <v>1.268</v>
+        <v>3.2858</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0767</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1912</v>
+        <v>3.3676</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1752</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1674</v>
+        <v>-0.6328</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3426</v>
+        <v>0.1091</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.435</v>
+        <v>-3.0451</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.1751</v>
+        <v>-4.3501</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6234</v>
+        <v>0.6748</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3425</v>
+        <v>-0.1574</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.281</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1952</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1952</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1579</v>
+        <v>-2.8832</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9217</v>
+        <v>-2.5238</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2362</v>
+        <v>-0.3595</v>
       </c>
       <c r="G12" t="n">
         <v>-1.8755</v>
@@ -1390,13 +1390,13 @@
         <v>0.87</v>
       </c>
       <c r="S12" t="n">
-        <v>1.7828</v>
+        <v>1.0575</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0227</v>
+        <v>0.4206</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7602</v>
+        <v>0.6369</v>
       </c>
       <c r="V12" t="n">
         <v>-0.7602</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>34.41230000000001</v>
+        <v>35.09719999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>22.7317</v>
+        <v>23.4166</v>
       </c>
       <c r="F13" t="n">
-        <v>11.6806</v>
+        <v>11.6808</v>
       </c>
       <c r="G13" t="n">
         <v>24.795</v>
@@ -1459,7 +1459,7 @@
         <v>0.3462999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>9.99999999995449e-05</v>
+        <v>9.999999999998899e-05</v>
       </c>
       <c r="Q13" t="n">
         <v>-15.2255</v>
@@ -1468,13 +1468,13 @@
         <v>15.2255</v>
       </c>
       <c r="S13" t="n">
-        <v>8.1174</v>
+        <v>8.8026</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2858</v>
+        <v>1.9708</v>
       </c>
       <c r="U13" t="n">
-        <v>6.8314</v>
+        <v>6.8315</v>
       </c>
       <c r="V13" t="n">
         <v>1.4999</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. CARRALERO MARTIN</t>
+          <t>A. CHAPELA LAGE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4299</v>
+        <v>1.5383</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0046</v>
+        <v>1.3696</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5747</v>
+        <v>0.1688</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.6277</v>
+        <v>0.7085</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.6116</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.0161</v>
+        <v>0.7969000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.0274</v>
+        <v>1.7573</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0547</v>
+        <v>0.876</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.0822</v>
+        <v>0.8813</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.6003</v>
+        <v>-1.0488</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6663</v>
+        <v>-0.9643</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9339</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>0.435</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
+        <v>-1.305</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.305</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0.3001</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.2127</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0.08740000000000001</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X14" t="n">
         <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="S14" t="n">
-        <v>-0.07190000000000001</v>
-      </c>
-      <c r="T14" t="n">
-        <v>-0.4879</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0.416</v>
-      </c>
-      <c r="V14" t="n">
-        <v>4.6944</v>
-      </c>
-      <c r="W14" t="n">
-        <v>4.5199</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0.1745</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. CHAPELA LAGE</t>
+          <t>J. CARRALERO MARTIN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2339</v>
+        <v>1.3798</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0343</v>
+        <v>1.8928</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1996</v>
+        <v>-0.513</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7085</v>
+        <v>-3.6277</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.08840000000000001</v>
+        <v>-0.6116</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7969000000000001</v>
+        <v>-3.0161</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7573</v>
+        <v>-2.0274</v>
       </c>
       <c r="K15" t="n">
-        <v>0.876</v>
+        <v>0.0547</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8813</v>
+        <v>-2.0822</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0488</v>
+        <v>-1.6003</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9643</v>
+        <v>-0.6663</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.9339</v>
       </c>
       <c r="P15" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="Q15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-1.305</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.305</v>
+        <v>0.435</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6046</v>
+        <v>-0.122</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.548</v>
+        <v>-0.5996</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0566</v>
+        <v>0.4777</v>
       </c>
       <c r="V15" t="n">
-        <v>1.13</v>
+        <v>4.6944</v>
       </c>
       <c r="W15" t="n">
-        <v>1.13</v>
+        <v>4.5199</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.1745</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. HOLLOWELL</t>
+          <t>H. ATENCIA SUAREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.6673</v>
+        <v>-2.378</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1371</v>
+        <v>0.6171</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.5302</v>
+        <v>-2.9951</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1231</v>
+        <v>-1.2129</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5414</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4184</v>
+        <v>-0.5984</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3424</v>
+        <v>2.2808</v>
       </c>
       <c r="K16" t="n">
-        <v>0.073</v>
+        <v>1.6274</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2694</v>
+        <v>0.6535</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4654</v>
+        <v>-3.4937</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6143999999999999</v>
+        <v>-2.2418</v>
       </c>
       <c r="O16" t="n">
-        <v>0.149</v>
+        <v>-1.2519</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2175</v>
+        <v>-0.435</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.3926</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2175</v>
+        <v>1.9576</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3066</v>
+        <v>-1.2951</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4795</v>
+        <v>-0.9661999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1729</v>
+        <v>-0.329</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.4552</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.695</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.4552</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H. ATENCIA SUAREZ</t>
+          <t>T. HOLLOWELL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.9548</v>
+        <v>-2.6981</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2818</v>
+        <v>-0.1371</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.2365</v>
+        <v>-2.561</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.2129</v>
+        <v>-0.1231</v>
       </c>
       <c r="H17" t="n">
+        <v>-0.5414</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.4184</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.2694</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-0.4654</v>
+      </c>
+      <c r="N17" t="n">
         <v>-0.6143999999999999</v>
       </c>
-      <c r="I17" t="n">
-        <v>-0.5984</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2.2808</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1.6274</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.6535</v>
-      </c>
-      <c r="M17" t="n">
-        <v>-3.4937</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-2.2418</v>
-      </c>
       <c r="O17" t="n">
-        <v>-1.2519</v>
+        <v>0.149</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.435</v>
+        <v>0.2175</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3926</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9576</v>
+        <v>0.2175</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.8719</v>
+        <v>-0.3374</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3014</v>
+        <v>-0.4795</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5705</v>
+        <v>0.1421</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5649999999999999</v>
+        <v>-2.4552</v>
       </c>
       <c r="W17" t="n">
-        <v>1.695</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.13</v>
+        <v>-2.4552</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.1491</v>
+        <v>-3.501</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.9892</v>
+        <v>-2.2127</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1599</v>
+        <v>-1.2883</v>
       </c>
       <c r="G18" t="n">
         <v>-2.3137</v>
@@ -1858,13 +1858,13 @@
         <v>1.7401</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1405</v>
+        <v>-0.4924</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3509</v>
+        <v>-0.5744</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2104</v>
+        <v>0.082</v>
       </c>
       <c r="V18" t="n">
         <v>-1.13</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.1562</v>
+        <v>-3.7587</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0704</v>
+        <v>1.2881</v>
       </c>
       <c r="F19" t="n">
-        <v>-5.2267</v>
+        <v>-5.0468</v>
       </c>
       <c r="G19" t="n">
         <v>-3.1434</v>
@@ -1936,13 +1936,13 @@
         <v>1.5225</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0564</v>
+        <v>-0.6588000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2572</v>
+        <v>-0.5251</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3135</v>
+        <v>-0.1337</v>
       </c>
       <c r="V19" t="n">
         <v>-1.479</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. COMENDADOR FEMENIAS</t>
+          <t>A. SCARIOLO ARES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.0476</v>
+        <v>-4.2862</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9541</v>
+        <v>-3.3079</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0935</v>
+        <v>-0.9782999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.375</v>
+        <v>-3.3252</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.214</v>
+        <v>-2.208</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.161</v>
+        <v>-1.1172</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3787</v>
+        <v>-1.7919</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.0672</v>
+        <v>-1.9067</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6885</v>
+        <v>0.1147</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.9963</v>
+        <v>-1.5333</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1468</v>
+        <v>-0.3013</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8495</v>
+        <v>-1.232</v>
       </c>
       <c r="P20" t="n">
-        <v>0.435</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4127</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4879</v>
+        <v>-0.6237</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0752</v>
+        <v>0.0324</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.695</v>
+        <v>-0.3698</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.695</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. SCARIOLO ARES</t>
+          <t>A. COMENDADOR FEMENIAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.8681</v>
+        <v>-4.3944</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.6432</v>
+        <v>-2.1776</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2249</v>
+        <v>-2.2168</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.3252</v>
+        <v>-2.375</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.208</v>
+        <v>-2.214</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1172</v>
+        <v>-0.161</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.7919</v>
+        <v>-0.3787</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.9067</v>
+        <v>-1.0672</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1147</v>
+        <v>0.6885</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5333</v>
+        <v>-1.9963</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3013</v>
+        <v>-1.1468</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.232</v>
+        <v>-0.8495</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.435</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1731</v>
+        <v>-0.7595</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9589</v>
+        <v>-0.7114</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2141</v>
+        <v>-0.0481</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3698</v>
+        <v>-1.695</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.2233</v>
+        <v>-4.9497</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.818</v>
+        <v>-2.4827</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.4054</v>
+        <v>-2.467</v>
       </c>
       <c r="G22" t="n">
         <v>-3.304</v>
@@ -2170,13 +2170,13 @@
         <v>1.305</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6371</v>
+        <v>-0.3635</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.4182</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1163</v>
+        <v>0.0547</v>
       </c>
       <c r="V22" t="n">
         <v>-1.4997</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I. MASSOUD RODRÍGUEZ</t>
+          <t>D. SANADZE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.486</v>
+        <v>-5.0702</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.9165</v>
+        <v>-2.2783</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5695</v>
+        <v>-2.7918</v>
       </c>
       <c r="G23" t="n">
-        <v>-6.2188</v>
+        <v>0.1401</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.2027</v>
+        <v>0.4867</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.0161</v>
+        <v>-0.3466</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.2605</v>
+        <v>3.6513</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.3259</v>
+        <v>2.2145</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.9347</v>
+        <v>1.4368</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.9582</v>
+        <v>-3.5112</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.8768</v>
+        <v>-1.7278</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.0814</v>
+        <v>-1.7834</v>
       </c>
       <c r="P23" t="n">
-        <v>1.305</v>
+        <v>-4.1326</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.305</v>
+        <v>-5.6552</v>
       </c>
       <c r="R23" t="n">
-        <v>2.6101</v>
+        <v>1.5225</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3118</v>
+        <v>-1.0776</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3509</v>
+        <v>-1.0346</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9609</v>
+        <v>-0.043</v>
       </c>
       <c r="V23" t="n">
-        <v>0.7395</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.7602</v>
       </c>
       <c r="X23" t="n">
-        <v>0.7395</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. SANADZE</t>
+          <t>I. MASSOUD RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.5236</v>
+        <v>-5.5489</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.6136</v>
+        <v>-4.2517</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.91</v>
+        <v>-1.2972</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1401</v>
+        <v>-6.2188</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4867</v>
+        <v>-3.2027</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3466</v>
+        <v>-3.0161</v>
       </c>
       <c r="J24" t="n">
-        <v>3.6513</v>
+        <v>-2.2605</v>
       </c>
       <c r="K24" t="n">
-        <v>2.2145</v>
+        <v>-1.3259</v>
       </c>
       <c r="L24" t="n">
-        <v>1.4368</v>
+        <v>-0.9347</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.5112</v>
+        <v>-3.9582</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.7278</v>
+        <v>-1.8768</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.7834</v>
+        <v>-2.0814</v>
       </c>
       <c r="P24" t="n">
-        <v>-4.1326</v>
+        <v>1.305</v>
       </c>
       <c r="Q24" t="n">
-        <v>-5.6552</v>
+        <v>-1.305</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5225</v>
+        <v>2.6101</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.5311</v>
+        <v>-1.3747</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.3699</v>
+        <v>-0.6862</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1612</v>
+        <v>-0.6886</v>
       </c>
       <c r="V24" t="n">
+        <v>0.7395</v>
+      </c>
+      <c r="W24" t="n">
         <v>0</v>
       </c>
-      <c r="W24" t="n">
-        <v>0.7602</v>
-      </c>
       <c r="X24" t="n">
-        <v>-0.7602</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-34.4122</v>
+        <v>-33.6671</v>
       </c>
       <c r="E25" t="n">
-        <v>-11.6806</v>
+        <v>-11.6804</v>
       </c>
       <c r="F25" t="n">
-        <v>-22.7317</v>
+        <v>-21.9865</v>
       </c>
       <c r="G25" t="n">
         <v>-24.7952</v>
@@ -2383,7 +2383,7 @@
         <v>0.6862000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.3464999999999996</v>
+        <v>-0.3464999999999997</v>
       </c>
       <c r="M25" t="n">
         <v>-25.1349</v>
@@ -2395,7 +2395,7 @@
         <v>-12.4193</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.0001000000000006551</v>
+        <v>-0.0001000000000004331</v>
       </c>
       <c r="Q25" t="n">
         <v>-15.2253</v>
@@ -2404,13 +2404,13 @@
         <v>15.2253</v>
       </c>
       <c r="S25" t="n">
-        <v>-8.117699999999999</v>
+        <v>-7.3723</v>
       </c>
       <c r="T25" t="n">
-        <v>-6.8316</v>
+        <v>-6.831600000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.286</v>
+        <v>-0.5409</v>
       </c>
       <c r="V25" t="n">
         <v>-1.4998</v>
